--- a/config/program_validation.xlsx
+++ b/config/program_validation.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VA Suicide Prevention — no SSVF fields</t>
+          <t>VA Suicide Prevention — blank all fields</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHIP program — RRH so Housed applies, has Legal</t>
+          <t>SHIP RRH — Legal and Housed pull through</t>
         </is>
       </c>
     </row>
@@ -600,7 +592,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDBG program</t>
+          <t>CDBG — blank all fields</t>
         </is>
       </c>
     </row>
@@ -635,19 +627,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>All EHA programs</t>
+          <t>All EHA programs — Legal and Housed pull through</t>
         </is>
       </c>
     </row>
